--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6400_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6400_SW2.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-04-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-04-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-05-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-05-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-06-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-06-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-04-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] no Air-Way row (FF6400 has no row of this size) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L8@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "L LGTH" = "1.480" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 537.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; ORB tip (overall); mapping: same-table check: 25/29 rows with an Air-Way value agree to rounding (4 differ, e.g. FS6400-06-06-O 1.25 vs 1.260); S5HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "H HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 537.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: same-table check: 27/29 rows with an Air-Way value agree to rounding (2 differ, e.g. FS6400-04-06-O 0.69 vs 0.750); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -10 = 0.875 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "B THREAD" "7/8-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "B THREAD" "7/8-14" in the table's format; L9@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L8@DRIVE 1.48 (Brennan) - Air-Way stud length 0.63 of ORB -10 (L8@DRIVE - L9@DRIVE on every Air-Way row of FS6400 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6400: FSM -04 bore on 5 Air-Way row(s): 0.18 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6400: ORB -10 bore on 5 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan] | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] no Air-Way row (FF6400 has no row of this size) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L8@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "L LGTH" = "1.480" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 537.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; ORB tip (overall); mapping: same-table check: 25/29 rows with an Air-Way value agree to rounding (4 differ, e.g. FS6400-06-06-O 1.25 vs 1.260); S5HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "H HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 537.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: same-table check: 27/29 rows with an Air-Way value agree to rounding (2 differ, e.g. FS6400-04-06-O 0.69 vs 0.750); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -10 = 0.875 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "B THREAD" "7/8-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p5 table ORFS-p005-t02 "FS6400-O MFS-MORB STRAIGHT" row FS6400-04-10-O col "B THREAD" "7/8-14" in the table's format; L9@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L8@DRIVE 1.48 (Brennan) - Air-Way stud length 0.63 of ORB -10 (L8@DRIVE - L9@DRIVE on every Air-Way row of FS6400 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6400: FSM -04 bore on 5 Air-Way row(s): 0.18 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6400: ORB -10 bore on 5 Air-Way row(s): 0.49 (unanimous) [Air-Way, not Brennan] | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-04-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-04-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-05-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-05-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-06-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-06-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-10-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-06-10-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-08-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-10-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-10-O (ORFS-p005-t02) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-10-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-08-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-08-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-10-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-10-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-12-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-12-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-20-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-16-20-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-16-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-20-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-20-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-24-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-20-24-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
